--- a/rooms.xlsx
+++ b/rooms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Featured listings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neighborhood guide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platforms" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tips" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Featured listings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Neighborhood guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Platforms" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tips" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,22 +464,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,45 +520,50 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Total /mo (incl 관리비)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Deposit</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Nearest station</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Commute to KHU</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Listing link</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Naver Map</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -566,57 +572,57 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Hoegi-dong full-option studio (KHU 2 min)</t>
+          <t>외대역 이문동 아늑한방</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>33m2 (English app)</t>
+          <t>33m2</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>Goshiwon</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>₩740,000 / mo  (₩170,000 / week)</t>
+          <t>₩411,667 / mo  (₩95,000 / week)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>₩330,000 (fixed)</t>
+          <t>₩411,667 / mo</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>13 m² (4 pyeong)</t>
+          <t>₩100,000</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn (Line 1 / Gyeongui-Jungang / Gyeongchun)</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>KHU back gate 2-min walk</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Bed, wardrobe, desk, fridge, microwave, washer, A/C, door-lock, CCTV; electricity+water+gas+internet ALL included</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -624,66 +630,71 @@
           <t>Open link</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Cheapest turnkey option right at the campus back gate. Min 2 weeks; 5% off for 8+ weeks. No ARC needed.</t>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Min 8 weeks.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Hoegi-dong full-option studio (KHU 2 min, larger)</t>
+          <t>외대역 이문동 아늑한방</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>33m2 (English app)</t>
+          <t>33m2</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>Goshiwon</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>₩880,000 / mo  (₩220,000 / week)</t>
+          <t>₩429,000 / mo  (₩99,000 / week)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>₩330,000 (fixed)</t>
+          <t>₩429,000 / mo</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>20 m² (6 pyeong)</t>
+          <t>₩100,000</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn (Line 1)</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>KHU back gate 2-min walk</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Bed, wardrobe, desk, fridge, microwave, gas range, washer, water purifier, A/C, WiFi; utilities ALL included</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
+          <t>Fridge, Washer, A/C, TV, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -691,66 +702,71 @@
           <t>Open link</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>More space, still walk-to-class. Min 2 weeks; 5% off for 8+ weeks.</t>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Min 8 weeks.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Hoegi / KHU open studio (deposit-based)</t>
+          <t>외창 미니룸 502호</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Daangn (당근, KR only)</t>
+          <t>33m2</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Open studio</t>
+          <t>Goshiwon</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>₩500,000 / mo</t>
+          <t>₩433,333 / mo  (₩100,000 / week)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>₩5,000,000</t>
+          <t>₩433,333 / mo</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>₩100,000</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn (Line 1)</t>
+          <t>7 m²</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>~10–15 min to KHU</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Full-option typical for the building</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>No — needs Korean or an agent; bring a helper</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
+          <t>TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -758,20 +774,5349 @@
           <t>Open link</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Lowest monthly rent IF the ₩5M deposit is affordable. Standard 1-yr leases; ask about a one-semester (short) contract.</t>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>햇빛잘드는 방</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>₩390,000 / mo  (₩90,000 / week)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>₩433,333 / mo</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>외창 원룸형 310호</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>외창 원룸형 407호</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>우디스테이 여성스탠다드</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>3 m²</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>우디 남성스탠다드내창</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>3 m²</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>외대역 아늑한원룸형</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>풀옵션원룸텔 206호</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>외대역 풀하우스아늑한방</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>₩524,333 / mo  (₩121,000 / week)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>₩524,333 / mo</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>외창 원룸형 204호</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>여성전용층원룸텔302호</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>~20–30 min to KHU</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>외창 원룸형 203호</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>원룸형 4층 402호</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>외대,경희대풀옵2인실B</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>₩498,333 / mo  (₩115,000 / week)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>₩585,000 / mo</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩86,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>경희대외대시립대풀옵션A</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>₩541,667 / mo  (₩125,000 / week)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>₩598,000 / mo</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Min 12 weeks. 관리비 ₩56,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>경희대풀옵션블루하우스E</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>₩606,667 / mo  (₩140,000 / week)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>₩606,667 / mo</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>우디스테이남디럭스내창C</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>₩606,667 / mo  (₩140,000 / week)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>₩606,667 / mo</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Room C-2</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>₩541,667 / mo  (₩125,000 / week)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>성지 707호</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>₩433,333 / mo  (₩100,000 / week)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>경희대회기역풀옵1인실C</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>3 m²</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>시립대 복도뷰 풀셋방</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>₩671,667 / mo  (₩155,000 / week)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>₩671,667 / mo</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 청량리역</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>여성 스위트 내창</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>우디스테이남성스위트내창</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>럭키하우스</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>₩606,667 / mo  (₩140,000 / week)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>₩693,334 / mo</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>20 m²</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks. 관리비 ₩86,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>한국외대경희대풀옵션C</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>₩585,000 / mo  (₩135,000 / week)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>₩715,000 / mo</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Room B</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>₩628,333 / mo  (₩145,000 / week)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>₩736,666 / mo</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>경희대 2분 풀옵션원룸</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Furnished studio</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시립대 복도뷰 풀셋방 </t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 청량리역</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>외대,경희대풀옵1인실A</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩86,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>외창 원룸</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>₩758,333 / mo  (₩175,000 / week)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>₩758,333 / mo</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>모던스테이 회기(회기역</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>₩758,333 / mo</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩65,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>모던스테이 회기a</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>₩758,333 / mo</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩65,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>깔끔 TV 비데 주차</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Furnished studio</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Induction, Bed, water included</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>고시텔로 외창방입니다</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, WiFi, all utilities included</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>시립대 전망뷰 풀셋방</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 청량리역</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2인실A(창가쪽)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>경희대회기역풀옵2인실A</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>경희대 외대 고려대</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>회기 이문 안암룸!</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Room A</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>₩801,666 / mo</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>특가 🛎️ 외대2분 풀옵</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Furnished studio</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>₩823,333 / mo</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>20 m²</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>외대앞역, 회기역</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>경희의료원 회기 원룸</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>₩823,333 / mo  (₩190,000 / week)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>₩823,333 / mo</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>회기 시립대 안암 원룸</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>₩823,333 / mo  (₩190,000 / week)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>₩823,333 / mo</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>회기역세권‼️B02😉</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>₩866,666 / mo</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>외대역도보3분 경희대</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>40 m²</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>성지 306호</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>성지 409호</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>스탠다드룸B</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>외대풀옵션외대앞1분깨끗</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>외대앞역, 회기역</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>성지 211</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>회기 경희대 316호</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>쉿🤫조용한픽셀하우스회기</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>회기삼육 조용한 독채</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>₩888,334 / mo</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>20 m²</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩151,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>1인실B</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>₩910,000 / mo</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>7 m²</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>회기 경희대 404호</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>₩910,000 / mo  (₩210,000 / week)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>₩910,000 / mo</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>아늑한방!!회기역8분</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>특가😲‼️ 회기역세권</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>20 m²</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>경희대2분 풀옵션원룸</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Furnished studio</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo  (₩220,000 / week)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>20 m²</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>시립대 전망뷰 풀셋큰방</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo  (₩220,000 / week)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 청량리역</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>회기역2분/경희대/외대</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>₩975,000 / mo  (₩225,000 / week)</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>₩975,000 / mo</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>편안한방😋경희대3분!</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>₩996,666 / mo</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>20 m²</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>성지 308호</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>₩996,667 / mo</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>경희대외대여성쉐어2인실</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>₩996,667 / mo</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>Min 4 weeks. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>성지 506호</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>₩996,667 / mo</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>경희대풀옵션블루하우스</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>₩996,667 / mo  (₩230,000 / week)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>₩996,667 / mo</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, A/C, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>외대풀옵션외대앞1분깨끗</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>₩996,667 / mo</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>17 m²</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>외대앞역, 회기역</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩260,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>1인실A</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>₩910,000 / mo  (₩210,000 / week)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>₩1,040,000 / mo</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>10 m²</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>🎈회기역 도보3분 넓음</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Furnished studio</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>₩910,000 / mo  (₩210,000 / week)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>₩1,083,333 / mo</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>23 m²</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>회기역, 외대앞역</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩173,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>디럭스룸 C</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>₩1,083,333 / mo  (₩250,000 / week)</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>₩1,083,333 / mo</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>디럭스룸 B</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>₩1,083,333 / mo  (₩250,000 / week)</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>₩1,083,333 / mo</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, TV, WiFi, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>성지 303호</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Goshiwon</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>₩1,083,334 / mo</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>₩100,000</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>13 m²</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>갬성있는방!!회기역8분</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Detached house</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>₩823,333 / mo  (₩190,000 / week)</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>₩1,126,666 / mo</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>23 m²</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>회기역</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>외대앞1분풀옵션외대깔끔</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>쉐어하우스</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>₩953,333 / mo  (₩220,000 / week)</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>₩1,170,000 / mo</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>₩330,000</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>26 m²</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>외대앞역, 회기역</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Yes — English app, foreign card OK</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rooms.xlsx
+++ b/rooms.xlsx
@@ -464,23 +464,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,65 +503,55 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Monthly rent</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Monthly rent</t>
+          <t>Total /mo</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Total /mo (incl 관리비)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Station</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Nearest station</t>
+          <t>Commute</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Commute to KHU</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Listing link</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Naver Map</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Listing link</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Naver Map</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -577,65 +565,55 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩498,333 / mo  (₩115,000 / week)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>₩498,333 / mo  (₩115,000 / week)</t>
+          <t>₩585,000 / mo</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>₩585,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>13 m²</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩86,667/mo included in total.</t>
         </is>
@@ -649,65 +627,55 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩541,667 / mo  (₩125,000 / week)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>₩541,667 / mo  (₩125,000 / week)</t>
+          <t>₩598,000 / mo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>₩598,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Min 12 weeks. 관리비 ₩56,333/mo included in total.</t>
         </is>
@@ -721,65 +689,55 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩541,667 / mo  (₩125,000 / week)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>₩541,667 / mo  (₩125,000 / week)</t>
+          <t>₩650,000 / mo</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
         </is>
@@ -793,65 +751,55 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩520,000 / mo  (₩120,000 / week)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>₩520,000 / mo  (₩120,000 / week)</t>
+          <t>₩650,000 / mo</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>3 m²</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>3 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -865,65 +813,55 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩606,667 / mo  (₩140,000 / week)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>₩606,667 / mo  (₩140,000 / week)</t>
+          <t>₩693,334 / mo</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>₩693,334 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Min 4 weeks. 관리비 ₩86,667/mo included in total.</t>
         </is>
@@ -937,65 +875,55 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩585,000 / mo  (₩135,000 / week)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>₩585,000 / mo  (₩135,000 / week)</t>
+          <t>₩715,000 / mo</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>₩715,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>13 m²</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -1009,65 +937,55 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩628,333 / mo  (₩145,000 / week)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>₩628,333 / mo  (₩145,000 / week)</t>
+          <t>₩736,666 / mo</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>₩736,666 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>7 m²</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>7 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
         </is>
@@ -1081,65 +999,55 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
+          <t>₩736,667 / mo</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>13 m²</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK.</t>
         </is>
@@ -1153,65 +1061,55 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩736,667 / mo</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩86,667/mo included in total.</t>
         </is>
@@ -1225,65 +1123,55 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
+          <t>₩780,000 / mo</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, TV, WiFi, Induction, Bed, water included</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
         </is>
@@ -1297,65 +1185,55 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩780,000 / mo</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>13 m²</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -1369,65 +1247,55 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩780,000 / mo</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>7 m²</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>7 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -1441,65 +1309,55 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>₩693,333 / mo  (₩160,000 / week)</t>
+          <t>₩801,666 / mo</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>₩801,666 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
         </is>
@@ -1513,65 +1371,55 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo  (₩180,000 / week)</t>
+          <t>₩823,333 / mo</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>₩823,333 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>외대앞역, 회기역</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>외대앞역, 회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
         </is>
@@ -1585,65 +1433,55 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>₩563,333 / mo  (₩130,000 / week)</t>
+          <t>₩866,666 / mo</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>₩866,666 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>13 m²</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
@@ -1657,65 +1495,55 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>₩866,667 / mo  (₩200,000 / week)</t>
+          <t>₩866,667 / mo</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>₩866,667 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>40 m²</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>40 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, TV, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK.</t>
         </is>
@@ -1729,65 +1557,55 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩866,667 / mo</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>₩866,667 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>외대앞역, 회기역</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>외대앞역, 회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
         </is>
@@ -1801,65 +1619,55 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
+          <t>₩888,334 / mo</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>₩888,334 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩151,667/mo included in total.</t>
         </is>
@@ -1873,65 +1681,55 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo  (₩180,000 / week)</t>
+          <t>₩910,000 / mo</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>₩910,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>7 m²</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>7 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -1945,65 +1743,55 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩953,333 / mo</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>₩953,333 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
@@ -2017,65 +1805,55 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩953,333 / mo</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>₩953,333 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
@@ -2089,65 +1867,55 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>₩953,333 / mo  (₩220,000 / week)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>₩953,333 / mo  (₩220,000 / week)</t>
+          <t>₩953,333 / mo</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>₩953,333 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK.</t>
         </is>
@@ -2161,65 +1929,55 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩975,000 / mo  (₩225,000 / week)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>₩975,000 / mo  (₩225,000 / week)</t>
+          <t>₩975,000 / mo</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>₩975,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK.</t>
         </is>
@@ -2233,65 +1991,55 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>₩693,333 / mo  (₩160,000 / week)</t>
+          <t>₩996,666 / mo</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>₩996,666 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
@@ -2305,65 +2053,55 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>₩866,667 / mo  (₩200,000 / week)</t>
+          <t>₩996,667 / mo</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>₩996,667 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>Min 4 weeks. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -2377,65 +2115,55 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
+          <t>₩996,667 / mo</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>₩996,667 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>외대앞역, 회기역</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>외대앞역, 회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩260,000/mo included in total.</t>
         </is>
@@ -2449,65 +2177,55 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩910,000 / mo  (₩210,000 / week)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>₩910,000 / mo  (₩210,000 / week)</t>
+          <t>₩1,040,000 / mo</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>₩1,040,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>10 m²</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
         </is>
@@ -2521,65 +2239,55 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>₩910,000 / mo  (₩210,000 / week)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>₩910,000 / mo  (₩210,000 / week)</t>
+          <t>₩1,083,333 / mo</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>₩1,083,333 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>23 m²</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>23 m²</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩173,333/mo included in total.</t>
         </is>
@@ -2593,65 +2301,55 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Detached house</t>
+          <t>₩823,333 / mo  (₩190,000 / week)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>₩823,333 / mo  (₩190,000 / week)</t>
+          <t>₩1,126,666 / mo</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>₩1,126,666 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>23 m²</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>23 m²</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
@@ -2665,65 +2363,55 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>33m2</t>
+          <t>쉐어하우스</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>₩953,333 / mo  (₩220,000 / week)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>₩953,333 / mo  (₩220,000 / week)</t>
+          <t>₩1,170,000 / mo</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>₩1,170,000 / mo</t>
+          <t>₩330,000</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>₩330,000</t>
+          <t>26 m²</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>26 m²</t>
+          <t>외대앞역, 회기역</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>외대앞역, 회기역</t>
+          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
           <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>Yes — English app, foreign card OK</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Open link</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>Min 1 week. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
         </is>
@@ -2731,66 +2419,66 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rooms.xlsx
+++ b/rooms.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -560,22 +560,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>외대,경희대풀옵2인실B</t>
+          <t>경희대 2분 풀옵션원룸</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>₩498,333 / mo  (₩115,000 / week)</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>₩585,000 / mo</t>
+          <t>₩736,667 / mo</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -615,29 +615,29 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩86,667/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>경희대외대시립대풀옵션A</t>
+          <t>깔끔 TV 비데 주차</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>₩541,667 / mo  (₩125,000 / week)</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>₩598,000 / mo</t>
+          <t>₩780,000 / mo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, TV, WiFi, Induction, Bed, water included</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -677,29 +677,29 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Min 12 weeks. 관리비 ₩56,333/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Room C-2</t>
+          <t>특가 🛎️ 외대2분 풀옵</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>₩541,667 / mo  (₩125,000 / week)</t>
+          <t>₩780,000 / mo  (₩180,000 / week)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo</t>
+          <t>₩823,333 / mo</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>외대앞역, 회기역</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -739,29 +739,29 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>경희대회기역풀옵1인실C</t>
+          <t>회기역세권‼️B02😉</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>₩520,000 / mo  (₩120,000 / week)</t>
+          <t>₩563,333 / mo  (₩130,000 / week)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo</t>
+          <t>₩866,666 / mo</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>3 m²</t>
+          <t>13 m²</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -801,29 +801,29 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>럭키하우스</t>
+          <t>외대역도보3분 경희대</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>₩606,667 / mo  (₩140,000 / week)</t>
+          <t>₩866,667 / mo  (₩200,000 / week)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>₩693,334 / mo</t>
+          <t>₩866,667 / mo</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>20 m²</t>
+          <t>40 m²</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>회기역, 외대앞역</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, TV, Induction, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -863,29 +863,29 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Min 4 weeks. 관리비 ₩86,667/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>한국외대경희대풀옵션C</t>
+          <t>회기삼육 조용한 독채</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>₩585,000 / mo  (₩135,000 / week)</t>
+          <t>₩736,667 / mo  (₩170,000 / week)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>₩715,000 / mo</t>
+          <t>₩888,334 / mo</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, Gas range, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -925,29 +925,29 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩151,667/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Room B</t>
+          <t>아늑한방!!회기역8분</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>₩628,333 / mo  (₩145,000 / week)</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>₩736,666 / mo</t>
+          <t>₩953,333 / mo</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>7 m²</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -987,29 +987,29 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>경희대 2분 풀옵션원룸</t>
+          <t>특가😲‼️ 회기역세권</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
+          <t>₩650,000 / mo  (₩150,000 / week)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo</t>
+          <t>₩953,333 / mo</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1049,29 +1049,29 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK.</t>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>외대,경희대풀옵1인실A</t>
+          <t>경희대2분 풀옵션원룸</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩953,333 / mo  (₩220,000 / week)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo</t>
+          <t>₩953,333 / mo</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>10 m²</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1111,29 +1111,29 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩86,667/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>깔끔 TV 비데 주차</t>
+          <t>편안한방😋경희대3분!</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Furnished studio</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
+          <t>₩693,333 / mo  (₩160,000 / week)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo</t>
+          <t>₩996,666 / mo</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>17 m²</t>
+          <t>20 m²</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>회기역</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, TV, WiFi, Induction, Bed, water included</t>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1173,29 +1173,29 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2인실A(창가쪽)</t>
+          <t>🎈회기역 도보3분 넓음</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Furnished studio</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩910,000 / mo  (₩210,000 / week)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo</t>
+          <t>₩1,083,333 / mo</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>13 m²</t>
+          <t>23 m²</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1235,29 +1235,29 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK. 관리비 ₩173,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>경희대회기역풀옵2인실A</t>
+          <t>갬성있는방!!회기역8분</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>쉐어하우스</t>
+          <t>Detached house</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
+          <t>₩823,333 / mo  (₩190,000 / week)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>₩780,000 / mo</t>
+          <t>₩1,126,666 / mo</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>7 m²</t>
+          <t>23 m²</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
+          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1297,1123 +1297,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Room A</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>₩693,333 / mo  (₩160,000 / week)</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>₩801,666 / mo</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>10 m²</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Min 11 weeks. 관리비 ₩108,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>특가 🛎️ 외대2분 풀옵</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Furnished studio</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>₩780,000 / mo  (₩180,000 / week)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>₩823,333 / mo</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>20 m²</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>외대앞역, 회기역</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>회기역세권‼️B02😉</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>₩563,333 / mo  (₩130,000 / week)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>₩866,666 / mo</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>13 m²</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
           <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>외대역도보3분 경희대</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>₩866,667 / mo  (₩200,000 / week)</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>₩866,667 / mo</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>40 m²</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, TV, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>외대풀옵션외대앞1분깨끗</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>₩866,667 / mo</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>17 m²</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>외대앞역, 회기역</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>회기삼육 조용한 독채</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>₩888,334 / mo</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>20 m²</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩151,667/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>1인실B</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>₩780,000 / mo  (₩180,000 / week)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>₩910,000 / mo</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>7 m²</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>아늑한방!!회기역8분</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>₩953,333 / mo</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>17 m²</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>특가😲‼️ 회기역세권</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>₩650,000 / mo  (₩150,000 / week)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>₩953,333 / mo</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>20 m²</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>경희대2분 풀옵션원룸</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Furnished studio</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>₩953,333 / mo  (₩220,000 / week)</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>₩953,333 / mo</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>20 m²</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Min 2 weeks. Short-stay OK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>회기역2분/경희대/외대</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>₩975,000 / mo  (₩225,000 / week)</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>₩975,000 / mo</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>10 m²</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>편안한방😋경희대3분!</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>₩693,333 / mo  (₩160,000 / week)</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>₩996,666 / mo</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>20 m²</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>경희대외대여성쉐어2인실</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>₩866,667 / mo  (₩200,000 / week)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>₩996,667 / mo</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>17 m²</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Min 4 weeks. 관리비 ₩130,000/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>외대풀옵션외대앞1분깨끗</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>₩736,667 / mo  (₩170,000 / week)</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>₩996,667 / mo</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>17 m²</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>외대앞역, 회기역</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩260,000/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>1인실A</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>₩910,000 / mo  (₩210,000 / week)</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>₩1,040,000 / mo</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>10 m²</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩130,000/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>🎈회기역 도보3분 넓음</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Furnished studio</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>₩910,000 / mo  (₩210,000 / week)</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>₩1,083,333 / mo</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>23 m²</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>회기역, 외대앞역</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, TV, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩173,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>갬성있는방!!회기역8분</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Detached house</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>₩823,333 / mo  (₩190,000 / week)</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>₩1,126,666 / mo</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>23 m²</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>회기역</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Induction, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>외대앞1분풀옵션외대깔끔</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>쉐어하우스</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>₩953,333 / mo  (₩220,000 / week)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>₩1,170,000 / mo</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>₩330,000</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>26 m²</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>외대앞역, 회기역</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Hoegi Stn, ~15 min walk or bus to KHU</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Fridge, Washer, A/C, WiFi, Gas range, Bed, all utilities included</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Open link</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩216,667/mo included in total.</t>
         </is>
       </c>
     </row>
@@ -2443,42 +1327,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rooms.xlsx
+++ b/rooms.xlsx
@@ -560,12 +560,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 삼선동5가</t>
+          <t>House, Samseon-dong 5-ga</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -590,17 +590,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>보문역</t>
+          <t>Bomun Stn</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Near 보문역</t>
+          <t>Near Bomun Stn</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 가스레인지</t>
+          <t>A/C, Washer, Fridge, Gas range</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -622,12 +622,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -684,12 +684,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -746,12 +746,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -808,12 +808,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 옷장, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Wardrobe, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1056,12 +1056,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1086,17 +1086,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1118,12 +1118,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 옷장, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Wardrobe, Fridge, Induction</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1210,17 +1210,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1242,12 +1242,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>회기역 (경춘선)</t>
+          <t>Hoegi Stn (Gyeongchun)</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역 (경춘선)</t>
+          <t>Near Hoegi Stn (Gyeongchun)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>전자레인지, 옷장, 침대, 에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>Microwave, Wardrobe, Bed, A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1304,12 +1304,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 용두동</t>
+          <t>House, Yongdu-dong</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>제기동역</t>
+          <t>Jegi-dong Stn</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Near 제기동역</t>
+          <t>Near Jegi-dong Stn</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1428,12 +1428,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 용두동</t>
+          <t>House, Yongdu-dong</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>청량리역</t>
+          <t>Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Near 청량리역</t>
+          <t>Near Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>가스레인지</t>
+          <t>Gas range</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 청량리동</t>
+          <t>House, Cheongnyangni-dong</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1676,12 +1676,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 냉장고, 가스레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Fridge, Gas range, Smart lock</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 청량리동</t>
+          <t>House, Cheongnyangni-dong</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>청량리역</t>
+          <t>Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Near 청량리역</t>
+          <t>Near Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>제기동역</t>
+          <t>Jegi-dong Stn</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Near 제기동역</t>
+          <t>Near Jegi-dong Stn</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1986,12 +1986,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>제기동역</t>
+          <t>Jegi-dong Stn</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Near 제기동역</t>
+          <t>Near Jegi-dong Stn</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2048,12 +2048,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2078,17 +2078,17 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 옷장, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Wardrobe, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2110,12 +2110,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2140,17 +2140,17 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -2172,12 +2172,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2202,17 +2202,17 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2234,12 +2234,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2296,12 +2296,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>청량리역</t>
+          <t>Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Near 청량리역</t>
+          <t>Near Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2358,12 +2358,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 상월곡동</t>
+          <t>House, Sangwolgok-dong</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>상월곡역</t>
+          <t>Sangwolgok Stn</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Near 상월곡역</t>
+          <t>Near Sangwolgok Stn</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 냉장고, 전자레인지</t>
+          <t>A/C, Washer, Bed, Desk, Fridge, Microwave</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2420,12 +2420,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2450,17 +2450,17 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2482,12 +2482,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2512,17 +2512,17 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 침대, 책상, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Bed, Desk, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 가스레인지</t>
+          <t>A/C, Washer, Fridge, Gas range</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2606,12 +2606,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 월계동</t>
+          <t>House, Wolgye-dong</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>월계역</t>
+          <t>Wolgye Stn</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Near 월계역</t>
+          <t>Near Wolgye Stn</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2698,17 +2698,17 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>신발장, 침대, 에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>Shoe rack, Bed, A/C, Washer, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2730,12 +2730,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>신발장, 침대, 에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>Shoe rack, Bed, A/C, Washer, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2792,12 +2792,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Induction</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2884,17 +2884,17 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Induction</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2916,12 +2916,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 상월곡동</t>
+          <t>House, Sangwolgok-dong</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Bed, Desk, Fridge, Induction</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2978,12 +2978,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3008,17 +3008,17 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -3040,12 +3040,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>기타, 이문동</t>
+          <t>Other, Imun-dong</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3070,17 +3070,17 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 상월곡동</t>
+          <t>House, Sangwolgok-dong</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3132,17 +3132,17 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>상월곡역</t>
+          <t>Sangwolgok Stn</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Near 상월곡역</t>
+          <t>Near Sangwolgok Stn</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 신발장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Shoe rack, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -3164,12 +3164,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3194,17 +3194,17 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -3226,12 +3226,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 가스레인지</t>
+          <t>A/C, Washer, Fridge, Gas range</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3288,12 +3288,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 가스레인지, 전자레인지, 전자도어락, 베란다</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Gas range, Microwave, Smart lock, Balcony</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3350,12 +3350,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -3412,12 +3412,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -3474,12 +3474,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3504,17 +3504,17 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3536,12 +3536,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3628,17 +3628,17 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 가스레인지, 전자도어락</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Gas range, Smart lock</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3660,12 +3660,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -3722,12 +3722,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 가스레인지</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Gas range</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -3784,12 +3784,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3814,17 +3814,17 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Desk, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3846,12 +3846,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -3908,12 +3908,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>의자, 인덕션, 책상, 옷장, 침대, 에어컨, 세탁기, 냉장고</t>
+          <t>Chair, Induction, Desk, Wardrobe, Bed, A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -3970,12 +3970,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -4032,12 +4032,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4062,17 +4062,17 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -4094,12 +4094,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>제기동역</t>
+          <t>Jegi-dong Stn</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Near 제기동역</t>
+          <t>Near Jegi-dong Stn</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -4156,12 +4156,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4186,17 +4186,17 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -4218,12 +4218,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>침대, 에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>Bed, A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -4280,12 +4280,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 하월곡동</t>
+          <t>House, Hawolgok-dong</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -4372,17 +4372,17 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
@@ -4404,12 +4404,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 가스레인지, 다용도실</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Gas range, Utility room</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -4466,12 +4466,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 가스레인지</t>
+          <t>A/C, Washer, Fridge, Gas range</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
@@ -4528,12 +4528,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -4590,12 +4590,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>청량리역</t>
+          <t>Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Near 청량리역</t>
+          <t>Near Cheongnyangni Stn</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4682,17 +4682,17 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 의자, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Bed, Chair, Fridge, Induction</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
@@ -4714,12 +4714,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4744,17 +4744,17 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 가스레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Gas range, Smart lock</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -4776,12 +4776,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4806,17 +4806,17 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Desk, Wardrobe, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -4838,12 +4838,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -4900,12 +4900,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -5024,12 +5024,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -5054,17 +5054,17 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -5086,12 +5086,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
@@ -5148,12 +5148,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -5210,12 +5210,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -5272,12 +5272,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -5334,12 +5334,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -5364,17 +5364,17 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
@@ -5396,12 +5396,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5426,17 +5426,17 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 옷장, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Wardrobe, Fridge, Induction</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
@@ -5458,12 +5458,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
@@ -5520,12 +5520,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5550,17 +5550,17 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -5612,17 +5612,17 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Induction</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -5644,12 +5644,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5674,17 +5674,17 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -5736,17 +5736,17 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -5768,12 +5768,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -5830,12 +5830,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -5892,12 +5892,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5922,17 +5922,17 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 가스레인지, 베란다</t>
+          <t>A/C, Washer, Fridge, Gas range, Balcony</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
@@ -5954,12 +5954,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 안암동5가</t>
+          <t>House, Anam-dong 5-ga</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -6016,12 +6016,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -6046,17 +6046,17 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -6078,12 +6078,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -6108,17 +6108,17 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
@@ -6140,12 +6140,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 석관동</t>
+          <t>House, Seokgwan-dong</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>신이문역</t>
+          <t>Sinimun Stn</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Near 신이문역</t>
+          <t>Near Sinimun Stn</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -6202,12 +6202,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -6232,17 +6232,17 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -6264,12 +6264,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -6356,17 +6356,17 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 옷장, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Wardrobe, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
@@ -6388,12 +6388,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 베란다</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Balcony</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
@@ -6450,12 +6450,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락, 베란다</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock, Balcony</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
@@ -6512,12 +6512,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -6542,17 +6542,17 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -6574,12 +6574,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -6604,17 +6604,17 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
@@ -6636,12 +6636,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
@@ -6698,12 +6698,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -6728,17 +6728,17 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
@@ -6760,12 +6760,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -6822,12 +6822,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
@@ -6884,12 +6884,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -6946,12 +6946,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -7008,12 +7008,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
@@ -7070,12 +7070,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -7100,17 +7100,17 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
@@ -7132,12 +7132,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -7162,17 +7162,17 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
@@ -7194,12 +7194,12 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -7224,17 +7224,17 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>인덕션, 세탁기, 에어컨, 냉장고</t>
+          <t>Induction, Washer, A/C, Fridge</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
@@ -7256,12 +7256,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -7318,12 +7318,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -7348,17 +7348,17 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 신발장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Shoe rack, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
@@ -7380,12 +7380,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -7410,17 +7410,17 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
@@ -7442,12 +7442,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -7472,17 +7472,17 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
@@ -7504,12 +7504,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
@@ -7566,12 +7566,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -7596,17 +7596,17 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 신발장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Shoe rack, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
@@ -7628,12 +7628,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 용두동</t>
+          <t>House, Yongdu-dong</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -7690,12 +7690,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -7752,12 +7752,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7782,17 +7782,17 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 가스레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Gas range, Smart lock</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
@@ -7814,12 +7814,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -7844,17 +7844,17 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
@@ -7876,12 +7876,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 가스레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Gas range, Smart lock</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
@@ -7938,12 +7938,12 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -8030,17 +8030,17 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -8062,12 +8062,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 전농동</t>
+          <t>House, Jeonnong-dong</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -8124,12 +8124,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 용두동</t>
+          <t>House, Yongdu-dong</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>제기동역</t>
+          <t>Jegi-dong Stn</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>Near 제기동역</t>
+          <t>Near Jegi-dong Stn</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
@@ -8186,12 +8186,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -8216,17 +8216,17 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
@@ -8248,12 +8248,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -8310,12 +8310,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -8340,17 +8340,17 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
@@ -8372,12 +8372,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 용두동</t>
+          <t>House, Yongdu-dong</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>제기동역</t>
+          <t>Jegi-dong Stn</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>Near 제기동역</t>
+          <t>Near Jegi-dong Stn</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -8434,12 +8434,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
@@ -8496,12 +8496,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>오피스텔, 제기동</t>
+          <t>Officetel, Jegi-dong</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>오피스텔</t>
+          <t>Officetel</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -8526,17 +8526,17 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>오피스텔, 제기동</t>
+          <t>Officetel, Jegi-dong</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>오피스텔</t>
+          <t>Officetel</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -8588,17 +8588,17 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
@@ -8620,12 +8620,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -8682,12 +8682,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -8712,17 +8712,17 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락, CCTV</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock, CCTV</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
@@ -8744,12 +8744,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>상가주택, 안암동5가</t>
+          <t>Commercial house, Anam-dong 5-ga</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>상가주택</t>
+          <t>Commercial house</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -8806,12 +8806,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -8836,17 +8836,17 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>침대, 에어컨, 세탁기, 냉장고</t>
+          <t>Bed, A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
@@ -8868,12 +8868,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -8898,17 +8898,17 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 냉장고, 전자레인지</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Fridge, Microwave</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
@@ -8930,12 +8930,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 안암동2가</t>
+          <t>House, Anam-dong 2-ga</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -8960,17 +8960,17 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>보문역</t>
+          <t>Bomun Stn</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Near 보문역</t>
+          <t>Near Bomun Stn</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 신발장, 냉장고, 가스레인지, 전자도어락, 베란다</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Shoe rack, Fridge, Gas range, Smart lock, Balcony</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
@@ -8992,12 +8992,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 보문동5가</t>
+          <t>House, Bomun-dong 5-ga</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>보문역</t>
+          <t>Bomun Stn</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>Near 보문역</t>
+          <t>Near Bomun Stn</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -9054,12 +9054,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -9084,17 +9084,17 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
@@ -9116,12 +9116,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -9178,12 +9178,12 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -9208,17 +9208,17 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 냉장고, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Fridge, Smart lock</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
@@ -9240,12 +9240,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -9270,17 +9270,17 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 책상, 냉장고, 가스레인지, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Desk, Fridge, Gas range, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
@@ -9302,12 +9302,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>오피스텔, 이문동</t>
+          <t>Officetel, Imun-dong</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>오피스텔</t>
+          <t>Officetel</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -9332,17 +9332,17 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
@@ -9364,12 +9364,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -9394,17 +9394,17 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
@@ -9426,12 +9426,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 안암동2가</t>
+          <t>House, Anam-dong 2-ga</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>보문역</t>
+          <t>Bomun Stn</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Near 보문역</t>
+          <t>Near Bomun Stn</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -9488,12 +9488,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
@@ -9550,12 +9550,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>신이문역</t>
+          <t>Sinimun Stn</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Near 신이문역</t>
+          <t>Near Sinimun Stn</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
@@ -9612,12 +9612,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -9642,17 +9642,17 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>세탁기</t>
+          <t>Washer</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
@@ -9674,12 +9674,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -9704,17 +9704,17 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
@@ -9736,12 +9736,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
@@ -9798,12 +9798,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>청량리역 (경의중앙선)</t>
+          <t>Cheongnyangni Stn (Gyeongui-Jungang)</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Near 청량리역 (경의중앙선)</t>
+          <t>Near Cheongnyangni Stn (Gyeongui-Jungang)</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
@@ -9860,12 +9860,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -9922,12 +9922,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
@@ -9984,12 +9984,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -10014,17 +10014,17 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 가스레인지</t>
+          <t>A/C, Washer, Fridge, Gas range</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
@@ -10046,12 +10046,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -10076,17 +10076,17 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
@@ -10108,7 +10108,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>특가 🛎️ 외대2분 풀옵</t>
+          <t>Deal: 2 min to HUFS, full-option</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>외대앞역, 회기역</t>
+          <t>HUFS Stn, Hoegi Stn</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -10163,19 +10163,19 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩43,333/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK. maint. fee ₩43,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -10200,17 +10200,17 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
@@ -10232,12 +10232,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -10262,17 +10262,17 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 옷장, 냉장고, 가스레인지, 전자도어락</t>
+          <t>A/C, Washer, Wardrobe, Fridge, Gas range, Smart lock</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
@@ -10294,12 +10294,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 안암동5가</t>
+          <t>House, Anam-dong 5-ga</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -10324,17 +10324,17 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>옷장, 침대, 에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>Wardrobe, Bed, A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
@@ -10356,12 +10356,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -10386,17 +10386,17 @@
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>침대, 에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>Bed, A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
@@ -10418,7 +10418,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>외대역도보3분 경희대</t>
+          <t>3 min walk to HUFS Stn · near KHU</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, HUFS Stn</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -10480,12 +10480,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -10542,7 +10542,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>회기삼육 조용한 독채</t>
+          <t>Quiet detached unit · Hoegi</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -10597,19 +10597,19 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩151,667/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK. maint. fee ₩151,667/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -10634,17 +10634,17 @@
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Microwave, Smart lock</t>
         </is>
       </c>
       <c r="J167" s="5" t="inlineStr">
@@ -10666,12 +10666,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -10696,17 +10696,17 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락, CCTV</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock, CCTV</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
@@ -10728,12 +10728,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -10758,17 +10758,17 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>고려대역</t>
+          <t>Korea Univ. Stn</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>Near 고려대역</t>
+          <t>Near Korea Univ. Stn</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
@@ -10790,12 +10790,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 안암동5가</t>
+          <t>House, Anam-dong 5-ga</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -10820,17 +10820,17 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
@@ -10852,12 +10852,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -10882,17 +10882,17 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 옷장, 냉장고, 인덕션, 전자도어락</t>
+          <t>A/C, Washer, Bed, Desk, Wardrobe, Fridge, Induction, Smart lock</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
@@ -10914,12 +10914,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 회기동</t>
+          <t>House, Hoegi-dong</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -10944,17 +10944,17 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J172" s="5" t="inlineStr">
@@ -10976,7 +10976,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>아늑한방!!회기역8분</t>
+          <t>Cozy room · 8 min to Hoegi Stn</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -11031,19 +11031,19 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. maint. fee ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -11068,17 +11068,17 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>신이문역</t>
+          <t>Sinimun Stn</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Near 신이문역</t>
+          <t>Near Sinimun Stn</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
@@ -11100,12 +11100,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 안암동2가</t>
+          <t>House, Anam-dong 2-ga</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -11130,17 +11130,17 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>보문역</t>
+          <t>Bomun Stn</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>Near 보문역</t>
+          <t>Near Bomun Stn</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J175" s="5" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>편안한방😋경희대3분!</t>
+          <t>Comfortable room · 3 min to KHU</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -11217,19 +11217,19 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. maint. fee ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -11254,17 +11254,17 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
@@ -11286,12 +11286,12 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -11316,17 +11316,17 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 침대, 책상, 의자, 옷장, 냉장고, 인덕션, 전자레인지, 전자도어락, 베란다</t>
+          <t>A/C, Washer, Bed, Desk, Chair, Wardrobe, Fridge, Induction, Microwave, Smart lock, Balcony</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
@@ -11348,12 +11348,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 종암동</t>
+          <t>House, Jongam-dong</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -11378,17 +11378,17 @@
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>월곡역</t>
+          <t>Wolgok Stn</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>Near 월곡역</t>
+          <t>Near Wolgok Stn</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>전자도어락, 에어컨, 세탁기, 냉장고, 인덕션</t>
+          <t>Smart lock, A/C, Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J179" s="5" t="inlineStr">
@@ -11410,12 +11410,12 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 보문동6가</t>
+          <t>House, Bomun-dong 6-ga</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -11440,12 +11440,12 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>창신역</t>
+          <t>Changshin Stn</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Near 창신역</t>
+          <t>Near Changshin Stn</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
@@ -11472,12 +11472,12 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 보문동6가</t>
+          <t>House, Bomun-dong 6-ga</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>창신역</t>
+          <t>Changshin Stn</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>Near 창신역</t>
+          <t>Near Changshin Stn</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -11534,7 +11534,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>🎈회기역 도보3분 넓음</t>
+          <t>Spacious · 3 min walk to Hoegi Stn</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>회기역, 외대앞역</t>
+          <t>Hoegi Stn, HUFS Stn</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -11589,19 +11589,19 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>Min 1 week. Short-stay OK. 관리비 ₩173,333/mo included in total.</t>
+          <t>Min 1 week. Short-stay OK. maint. fee ₩173,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 이문동</t>
+          <t>House, Imun-dong</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -11626,17 +11626,17 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>외대앞역</t>
+          <t>HUFS Stn</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>Near 외대앞역</t>
+          <t>Near HUFS Stn</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>세탁기, 냉장고, 인덕션</t>
+          <t>Washer, Fridge, Induction</t>
         </is>
       </c>
       <c r="J183" s="5" t="inlineStr">
@@ -11658,12 +11658,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 제기동</t>
+          <t>House, Jegi-dong</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -11688,17 +11688,17 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>안암역</t>
+          <t>Anam Stn</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>Near 안암역</t>
+          <t>Near Anam Stn</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>에어컨, 세탁기, 냉장고</t>
+          <t>A/C, Washer, Fridge</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
@@ -11720,7 +11720,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>갬성있는방!!회기역8분</t>
+          <t>Stylish room · 8 min to Hoegi Stn</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -11775,19 +11775,19 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>Min 2 weeks. Short-stay OK. 관리비 ₩303,333/mo included in total.</t>
+          <t>Min 2 weeks. Short-stay OK. maint. fee ₩303,333/mo included in total.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>일반주택, 휘경동</t>
+          <t>House, Hwigyeong-dong</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>일반주택</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -11812,12 +11812,12 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>회기역</t>
+          <t>Hoegi Stn</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>Near 회기역</t>
+          <t>Near Hoegi Stn</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
